--- a/artfynd/A 21253-2025 artfynd.xlsx
+++ b/artfynd/A 21253-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>65464958</v>
       </c>
       <c r="B2" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +700,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607618.7207334669</v>
+        <v>607619</v>
       </c>
       <c r="R2" t="n">
-        <v>7019136.919287137</v>
+        <v>7019137</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2016-07-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-07-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>65464955</v>
+        <v>65464952</v>
       </c>
       <c r="B3" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1205</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607609.9928994754</v>
+        <v>607627</v>
       </c>
       <c r="R3" t="n">
-        <v>7019195.61357599</v>
+        <v>7019207</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,21 +840,11 @@
           <t>2016-07-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-07-11</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -883,6 +853,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -899,15 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>65464960</v>
+        <v>65464957</v>
       </c>
       <c r="B4" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,12 +894,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607673.4920476812</v>
+        <v>607615</v>
       </c>
       <c r="R4" t="n">
-        <v>7019103.630759496</v>
+        <v>7019205</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +942,9 @@
           <t>2016-07-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2016-07-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>65464961</v>
+        <v>65464960</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607673.4920476812</v>
+        <v>607673</v>
       </c>
       <c r="R5" t="n">
-        <v>7019103.630759496</v>
+        <v>7019104</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1039,9 @@
           <t>2016-07-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2016-07-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,12 +1071,7 @@
         <v>65464954</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607615.397489895</v>
+        <v>607615</v>
       </c>
       <c r="R6" t="n">
-        <v>7019195.794464001</v>
+        <v>7019196</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1136,9 @@
           <t>2016-07-05</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2016-07-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,35 +1165,34 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>65464963</v>
+        <v>65464961</v>
       </c>
       <c r="B7" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223597</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1271,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>607686.1844773279</v>
+        <v>607673</v>
       </c>
       <c r="R7" t="n">
-        <v>7019047.769411306</v>
+        <v>7019104</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,19 +1233,9 @@
           <t>2016-07-05</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2016-07-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,37 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>65464962</v>
+        <v>65464955</v>
       </c>
       <c r="B8" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>1205</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1383,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>607673.4920476812</v>
+        <v>607610</v>
       </c>
       <c r="R8" t="n">
-        <v>7019103.630759496</v>
+        <v>7019196</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,19 +1330,9 @@
           <t>2016-07-05</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2016-07-11</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,15 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>65464957</v>
+        <v>65464962</v>
       </c>
       <c r="B9" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1471,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1495,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>607615.0964126833</v>
+        <v>607673</v>
       </c>
       <c r="R9" t="n">
-        <v>7019204.789850273</v>
+        <v>7019104</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,19 +1427,9 @@
           <t>2016-07-05</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2016-07-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1567,37 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>65464952</v>
+        <v>65464949</v>
       </c>
       <c r="B10" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1607,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>607627.1964840892</v>
+        <v>607539</v>
       </c>
       <c r="R10" t="n">
-        <v>7019206.995954747</v>
+        <v>7019444</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1640,21 +1524,11 @@
           <t>2016-07-05</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2016-07-11</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1663,11 +1537,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1687,12 +1556,7 @@
         <v>65464959</v>
       </c>
       <c r="B11" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>607660.2785690264</v>
+        <v>607660</v>
       </c>
       <c r="R11" t="n">
-        <v>7019121.199743068</v>
+        <v>7019121</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1757,19 +1621,9 @@
           <t>2016-07-05</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2016-07-11</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1793,6 +1647,99 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>65464963</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Forsmo-Näsåker, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>607686</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7019048</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2016-07-05</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2016-07-11</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21253-2025 artfynd.xlsx
+++ b/artfynd/A 21253-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65464958</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65464952</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65464957</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65464960</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65464954</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65464961</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65464955</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65464962</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65464949</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65464959</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1740,8 +1795,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65464963</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>